--- a/gauntlet/loop-1/workbooks-v1.7/DAMM-v1.7-Scoring-Workbook-Nigeria.xlsx
+++ b/gauntlet/loop-1/workbooks-v1.7/DAMM-v1.7-Scoring-Workbook-Nigeria.xlsx
@@ -2231,11 +2231,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="89508281"/>
-        <c:axId val="10051009"/>
+        <c:axId val="63304355"/>
+        <c:axId val="72140686"/>
       </c:radarChart>
       <c:catAx>
-        <c:axId val="89508281"/>
+        <c:axId val="63304355"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2265,7 +2265,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="10051009"/>
+        <c:crossAx val="72140686"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2273,7 +2273,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="10051009"/>
+        <c:axId val="72140686"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="5"/>
@@ -2318,7 +2318,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="89508281"/>
+        <c:crossAx val="63304355"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2538,11 +2538,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="39371182"/>
-        <c:axId val="39535345"/>
+        <c:axId val="51040965"/>
+        <c:axId val="1714291"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="39371182"/>
+        <c:axId val="51040965"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2575,7 +2575,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="39535345"/>
+        <c:crossAx val="1714291"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2583,7 +2583,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="39535345"/>
+        <c:axId val="1714291"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2626,7 +2626,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="39371182"/>
+        <c:crossAx val="51040965"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3200,11 +3200,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="99395977"/>
-        <c:axId val="79091286"/>
+        <c:axId val="7846832"/>
+        <c:axId val="55399197"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="99395977"/>
+        <c:axId val="7846832"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3237,7 +3237,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="79091286"/>
+        <c:crossAx val="55399197"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3245,7 +3245,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="79091286"/>
+        <c:axId val="55399197"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3288,7 +3288,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99395977"/>
+        <c:crossAx val="7846832"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3490,11 +3490,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="69589709"/>
-        <c:axId val="53347870"/>
+        <c:axId val="6168645"/>
+        <c:axId val="85058173"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="69589709"/>
+        <c:axId val="6168645"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3527,7 +3527,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="53347870"/>
+        <c:crossAx val="85058173"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3535,7 +3535,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="53347870"/>
+        <c:axId val="85058173"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="5"/>
@@ -3579,7 +3579,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="69589709"/>
+        <c:crossAx val="6168645"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3787,11 +3787,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="13790780"/>
-        <c:axId val="55228772"/>
+        <c:axId val="49680790"/>
+        <c:axId val="41194926"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="13790780"/>
+        <c:axId val="49680790"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3824,7 +3824,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="55228772"/>
+        <c:crossAx val="41194926"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3832,7 +3832,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="55228772"/>
+        <c:axId val="41194926"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3875,7 +3875,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="13790780"/>
+        <c:crossAx val="49680790"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4113,11 +4113,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="41548547"/>
-        <c:axId val="5549818"/>
+        <c:axId val="74957630"/>
+        <c:axId val="71234934"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="41548547"/>
+        <c:axId val="74957630"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4150,7 +4150,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="5549818"/>
+        <c:crossAx val="71234934"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4158,7 +4158,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="5549818"/>
+        <c:axId val="71234934"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4201,7 +4201,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="41548547"/>
+        <c:crossAx val="74957630"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>

--- a/gauntlet/loop-1/workbooks-v1.7/DAMM-v1.7-Scoring-Workbook-Nigeria.xlsx
+++ b/gauntlet/loop-1/workbooks-v1.7/DAMM-v1.7-Scoring-Workbook-Nigeria.xlsx
@@ -2231,11 +2231,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="63304355"/>
-        <c:axId val="72140686"/>
+        <c:axId val="45229842"/>
+        <c:axId val="30793250"/>
       </c:radarChart>
       <c:catAx>
-        <c:axId val="63304355"/>
+        <c:axId val="45229842"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2265,7 +2265,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="72140686"/>
+        <c:crossAx val="30793250"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2273,7 +2273,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="72140686"/>
+        <c:axId val="30793250"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="5"/>
@@ -2318,7 +2318,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="63304355"/>
+        <c:crossAx val="45229842"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2538,11 +2538,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="51040965"/>
-        <c:axId val="1714291"/>
+        <c:axId val="14402250"/>
+        <c:axId val="62540668"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="51040965"/>
+        <c:axId val="14402250"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2575,7 +2575,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1714291"/>
+        <c:crossAx val="62540668"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2583,7 +2583,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="1714291"/>
+        <c:axId val="62540668"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2626,7 +2626,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="51040965"/>
+        <c:crossAx val="14402250"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3200,11 +3200,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="7846832"/>
-        <c:axId val="55399197"/>
+        <c:axId val="3172254"/>
+        <c:axId val="66923422"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="7846832"/>
+        <c:axId val="3172254"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3237,7 +3237,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="55399197"/>
+        <c:crossAx val="66923422"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3245,7 +3245,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="55399197"/>
+        <c:axId val="66923422"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3288,7 +3288,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="7846832"/>
+        <c:crossAx val="3172254"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3490,11 +3490,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="6168645"/>
-        <c:axId val="85058173"/>
+        <c:axId val="563374"/>
+        <c:axId val="56354412"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="6168645"/>
+        <c:axId val="563374"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3527,7 +3527,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="85058173"/>
+        <c:crossAx val="56354412"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3535,7 +3535,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="85058173"/>
+        <c:axId val="56354412"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="5"/>
@@ -3579,7 +3579,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="6168645"/>
+        <c:crossAx val="563374"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3787,11 +3787,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="49680790"/>
-        <c:axId val="41194926"/>
+        <c:axId val="93719420"/>
+        <c:axId val="26044353"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="49680790"/>
+        <c:axId val="93719420"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3824,7 +3824,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="41194926"/>
+        <c:crossAx val="26044353"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3832,7 +3832,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="41194926"/>
+        <c:axId val="26044353"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3875,7 +3875,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="49680790"/>
+        <c:crossAx val="93719420"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4113,11 +4113,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="74957630"/>
-        <c:axId val="71234934"/>
+        <c:axId val="32929754"/>
+        <c:axId val="85818382"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="74957630"/>
+        <c:axId val="32929754"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4150,7 +4150,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="71234934"/>
+        <c:crossAx val="85818382"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4158,7 +4158,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="71234934"/>
+        <c:axId val="85818382"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4201,7 +4201,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74957630"/>
+        <c:crossAx val="32929754"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>

--- a/gauntlet/loop-1/workbooks-v1.7/DAMM-v1.7-Scoring-Workbook-Nigeria.xlsx
+++ b/gauntlet/loop-1/workbooks-v1.7/DAMM-v1.7-Scoring-Workbook-Nigeria.xlsx
@@ -192,7 +192,7 @@
     <t xml:space="preserve">Band: Nascent</t>
   </si>
   <si>
-    <t xml:space="preserve">1.0 – &lt;1.8</t>
+    <t xml:space="preserve">1.0 – &lt;1.5</t>
   </si>
   <si>
     <t xml:space="preserve">Half-open bands; a pillar band in parentheses means judged, gap and held rows outnumber the levelled measured and documented ones.</t>
@@ -201,25 +201,25 @@
     <t xml:space="preserve">Band: Emerging</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8 – &lt;2.6</t>
+    <t xml:space="preserve">1.5 – &lt;2.5</t>
   </si>
   <si>
     <t xml:space="preserve">Band: Established</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6 – &lt;3.4</t>
+    <t xml:space="preserve">2.5 – &lt;3.5</t>
   </si>
   <si>
     <t xml:space="preserve">Band: Advanced</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4 – &lt;4.2</t>
+    <t xml:space="preserve">3.5 – &lt;4.5</t>
   </si>
   <si>
     <t xml:space="preserve">Band: Transformative</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2 – 5.0</t>
+    <t xml:space="preserve">4.5 – 5.0</t>
   </si>
   <si>
     <t xml:space="preserve">Universal prerequisites</t>
@@ -2231,11 +2231,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="45229842"/>
-        <c:axId val="30793250"/>
+        <c:axId val="54620785"/>
+        <c:axId val="38812882"/>
       </c:radarChart>
       <c:catAx>
-        <c:axId val="45229842"/>
+        <c:axId val="54620785"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2265,7 +2265,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="30793250"/>
+        <c:crossAx val="38812882"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2273,7 +2273,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="30793250"/>
+        <c:axId val="38812882"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="5"/>
@@ -2318,7 +2318,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="45229842"/>
+        <c:crossAx val="54620785"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2538,11 +2538,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="14402250"/>
-        <c:axId val="62540668"/>
+        <c:axId val="41973315"/>
+        <c:axId val="90346970"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="14402250"/>
+        <c:axId val="41973315"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2575,7 +2575,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="62540668"/>
+        <c:crossAx val="90346970"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2583,7 +2583,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="62540668"/>
+        <c:axId val="90346970"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2626,7 +2626,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="14402250"/>
+        <c:crossAx val="41973315"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3200,11 +3200,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="3172254"/>
-        <c:axId val="66923422"/>
+        <c:axId val="48254809"/>
+        <c:axId val="11868081"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="3172254"/>
+        <c:axId val="48254809"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3237,7 +3237,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="66923422"/>
+        <c:crossAx val="11868081"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3245,7 +3245,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="66923422"/>
+        <c:axId val="11868081"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3288,7 +3288,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="3172254"/>
+        <c:crossAx val="48254809"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3490,11 +3490,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="563374"/>
-        <c:axId val="56354412"/>
+        <c:axId val="55379877"/>
+        <c:axId val="74667011"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="563374"/>
+        <c:axId val="55379877"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3527,7 +3527,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="56354412"/>
+        <c:crossAx val="74667011"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3535,7 +3535,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="56354412"/>
+        <c:axId val="74667011"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="5"/>
@@ -3579,7 +3579,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="563374"/>
+        <c:crossAx val="55379877"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3787,11 +3787,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="93719420"/>
-        <c:axId val="26044353"/>
+        <c:axId val="40908087"/>
+        <c:axId val="7955604"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="93719420"/>
+        <c:axId val="40908087"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3824,7 +3824,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="26044353"/>
+        <c:crossAx val="7955604"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3832,7 +3832,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="26044353"/>
+        <c:axId val="7955604"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3875,7 +3875,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="93719420"/>
+        <c:crossAx val="40908087"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4113,11 +4113,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="32929754"/>
-        <c:axId val="85818382"/>
+        <c:axId val="70172770"/>
+        <c:axId val="97576656"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="32929754"/>
+        <c:axId val="70172770"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4150,7 +4150,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="85818382"/>
+        <c:crossAx val="97576656"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4158,7 +4158,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="85818382"/>
+        <c:axId val="97576656"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4201,7 +4201,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="32929754"/>
+        <c:crossAx val="70172770"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11634,7 +11634,7 @@
         <v>2.25</v>
       </c>
       <c r="E66" s="9" t="str">
-        <f aca="false">IF($D66="","Not rated",IF((COUNTIFS($C$5:$C$61,$A66,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")+$I66+$J66)&gt;($C66-COUNTIFS($C$5:$C$61,$A66,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")),"("&amp;IF($D66&lt;1.8,"Nascent",IF($D66&lt;2.6,"Emerging",IF($D66&lt;3.4,"Established",IF($D66&lt;4.2,"Advanced","Transformative"))))&amp;")",IF($D66&lt;1.8,"Nascent",IF($D66&lt;2.6,"Emerging",IF($D66&lt;3.4,"Established",IF($D66&lt;4.2,"Advanced","Transformative"))))))</f>
+        <f aca="false">IF($D66="","Not rated",IF((COUNTIFS($C$5:$C$61,$A66,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")+$I66+$J66)&gt;($C66-COUNTIFS($C$5:$C$61,$A66,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")),"("&amp;IF($D66&lt;1.5,"Nascent",IF($D66&lt;2.5,"Emerging",IF($D66&lt;3.5,"Established",IF($D66&lt;4.5,"Advanced","Transformative"))))&amp;")",IF($D66&lt;1.5,"Nascent",IF($D66&lt;2.5,"Emerging",IF($D66&lt;3.5,"Established",IF($D66&lt;4.5,"Advanced","Transformative"))))))</f>
         <v>Emerging</v>
       </c>
       <c r="F66" s="15" t="n">
@@ -11679,7 +11679,7 @@
         <v>2.83</v>
       </c>
       <c r="E67" s="9" t="str">
-        <f aca="false">IF($D67="","Not rated",IF((COUNTIFS($C$5:$C$61,$A67,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")+$I67+$J67)&gt;($C67-COUNTIFS($C$5:$C$61,$A67,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")),"("&amp;IF($D67&lt;1.8,"Nascent",IF($D67&lt;2.6,"Emerging",IF($D67&lt;3.4,"Established",IF($D67&lt;4.2,"Advanced","Transformative"))))&amp;")",IF($D67&lt;1.8,"Nascent",IF($D67&lt;2.6,"Emerging",IF($D67&lt;3.4,"Established",IF($D67&lt;4.2,"Advanced","Transformative"))))))</f>
+        <f aca="false">IF($D67="","Not rated",IF((COUNTIFS($C$5:$C$61,$A67,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")+$I67+$J67)&gt;($C67-COUNTIFS($C$5:$C$61,$A67,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")),"("&amp;IF($D67&lt;1.5,"Nascent",IF($D67&lt;2.5,"Emerging",IF($D67&lt;3.5,"Established",IF($D67&lt;4.5,"Advanced","Transformative"))))&amp;")",IF($D67&lt;1.5,"Nascent",IF($D67&lt;2.5,"Emerging",IF($D67&lt;3.5,"Established",IF($D67&lt;4.5,"Advanced","Transformative"))))))</f>
         <v>Established</v>
       </c>
       <c r="F67" s="15" t="n">
@@ -11724,8 +11724,8 @@
         <v>2.57</v>
       </c>
       <c r="E68" s="9" t="str">
-        <f aca="false">IF($D68="","Not rated",IF((COUNTIFS($C$5:$C$61,$A68,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")+$I68+$J68)&gt;($C68-COUNTIFS($C$5:$C$61,$A68,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")),"("&amp;IF($D68&lt;1.8,"Nascent",IF($D68&lt;2.6,"Emerging",IF($D68&lt;3.4,"Established",IF($D68&lt;4.2,"Advanced","Transformative"))))&amp;")",IF($D68&lt;1.8,"Nascent",IF($D68&lt;2.6,"Emerging",IF($D68&lt;3.4,"Established",IF($D68&lt;4.2,"Advanced","Transformative"))))))</f>
-        <v>Emerging</v>
+        <f aca="false">IF($D68="","Not rated",IF((COUNTIFS($C$5:$C$61,$A68,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")+$I68+$J68)&gt;($C68-COUNTIFS($C$5:$C$61,$A68,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")),"("&amp;IF($D68&lt;1.5,"Nascent",IF($D68&lt;2.5,"Emerging",IF($D68&lt;3.5,"Established",IF($D68&lt;4.5,"Advanced","Transformative"))))&amp;")",IF($D68&lt;1.5,"Nascent",IF($D68&lt;2.5,"Emerging",IF($D68&lt;3.5,"Established",IF($D68&lt;4.5,"Advanced","Transformative"))))))</f>
+        <v>Established</v>
       </c>
       <c r="F68" s="15" t="n">
         <f aca="false">COUNTIFS($C$5:$C$61,$A68,$S$5:$S$61,"Measured")</f>
@@ -11769,7 +11769,7 @@
         <v>2.88</v>
       </c>
       <c r="E69" s="9" t="str">
-        <f aca="false">IF($D69="","Not rated",IF((COUNTIFS($C$5:$C$61,$A69,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")+$I69+$J69)&gt;($C69-COUNTIFS($C$5:$C$61,$A69,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")),"("&amp;IF($D69&lt;1.8,"Nascent",IF($D69&lt;2.6,"Emerging",IF($D69&lt;3.4,"Established",IF($D69&lt;4.2,"Advanced","Transformative"))))&amp;")",IF($D69&lt;1.8,"Nascent",IF($D69&lt;2.6,"Emerging",IF($D69&lt;3.4,"Established",IF($D69&lt;4.2,"Advanced","Transformative"))))))</f>
+        <f aca="false">IF($D69="","Not rated",IF((COUNTIFS($C$5:$C$61,$A69,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")+$I69+$J69)&gt;($C69-COUNTIFS($C$5:$C$61,$A69,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")),"("&amp;IF($D69&lt;1.5,"Nascent",IF($D69&lt;2.5,"Emerging",IF($D69&lt;3.5,"Established",IF($D69&lt;4.5,"Advanced","Transformative"))))&amp;")",IF($D69&lt;1.5,"Nascent",IF($D69&lt;2.5,"Emerging",IF($D69&lt;3.5,"Established",IF($D69&lt;4.5,"Advanced","Transformative"))))))</f>
         <v>Established</v>
       </c>
       <c r="F69" s="15" t="n">
@@ -11814,8 +11814,8 @@
         <v>2.5</v>
       </c>
       <c r="E70" s="9" t="str">
-        <f aca="false">IF($D70="","Not rated",IF((COUNTIFS($C$5:$C$61,$A70,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")+$I70+$J70)&gt;($C70-COUNTIFS($C$5:$C$61,$A70,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")),"("&amp;IF($D70&lt;1.8,"Nascent",IF($D70&lt;2.6,"Emerging",IF($D70&lt;3.4,"Established",IF($D70&lt;4.2,"Advanced","Transformative"))))&amp;")",IF($D70&lt;1.8,"Nascent",IF($D70&lt;2.6,"Emerging",IF($D70&lt;3.4,"Established",IF($D70&lt;4.2,"Advanced","Transformative"))))))</f>
-        <v>Emerging</v>
+        <f aca="false">IF($D70="","Not rated",IF((COUNTIFS($C$5:$C$61,$A70,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")+$I70+$J70)&gt;($C70-COUNTIFS($C$5:$C$61,$A70,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")),"("&amp;IF($D70&lt;1.5,"Nascent",IF($D70&lt;2.5,"Emerging",IF($D70&lt;3.5,"Established",IF($D70&lt;4.5,"Advanced","Transformative"))))&amp;")",IF($D70&lt;1.5,"Nascent",IF($D70&lt;2.5,"Emerging",IF($D70&lt;3.5,"Established",IF($D70&lt;4.5,"Advanced","Transformative"))))))</f>
+        <v>Established</v>
       </c>
       <c r="F70" s="15" t="n">
         <f aca="false">COUNTIFS($C$5:$C$61,$A70,$S$5:$S$61,"Measured")</f>
@@ -11859,8 +11859,8 @@
         <v>2.56</v>
       </c>
       <c r="E71" s="9" t="str">
-        <f aca="false">IF($D71="","Not rated",IF((COUNTIFS($C$5:$C$61,$A71,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")+$I71+$J71)&gt;($C71-COUNTIFS($C$5:$C$61,$A71,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")),"("&amp;IF($D71&lt;1.8,"Nascent",IF($D71&lt;2.6,"Emerging",IF($D71&lt;3.4,"Established",IF($D71&lt;4.2,"Advanced","Transformative"))))&amp;")",IF($D71&lt;1.8,"Nascent",IF($D71&lt;2.6,"Emerging",IF($D71&lt;3.4,"Established",IF($D71&lt;4.2,"Advanced","Transformative"))))))</f>
-        <v>Emerging</v>
+        <f aca="false">IF($D71="","Not rated",IF((COUNTIFS($C$5:$C$61,$A71,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")+$I71+$J71)&gt;($C71-COUNTIFS($C$5:$C$61,$A71,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")),"("&amp;IF($D71&lt;1.5,"Nascent",IF($D71&lt;2.5,"Emerging",IF($D71&lt;3.5,"Established",IF($D71&lt;4.5,"Advanced","Transformative"))))&amp;")",IF($D71&lt;1.5,"Nascent",IF($D71&lt;2.5,"Emerging",IF($D71&lt;3.5,"Established",IF($D71&lt;4.5,"Advanced","Transformative"))))))</f>
+        <v>Established</v>
       </c>
       <c r="F71" s="15" t="n">
         <f aca="false">COUNTIFS($C$5:$C$61,$A71,$S$5:$S$61,"Measured")</f>
@@ -11904,7 +11904,7 @@
         <v>3.25</v>
       </c>
       <c r="E72" s="9" t="str">
-        <f aca="false">IF($D72="","Not rated",IF((COUNTIFS($C$5:$C$61,$A72,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")+$I72+$J72)&gt;($C72-COUNTIFS($C$5:$C$61,$A72,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")),"("&amp;IF($D72&lt;1.8,"Nascent",IF($D72&lt;2.6,"Emerging",IF($D72&lt;3.4,"Established",IF($D72&lt;4.2,"Advanced","Transformative"))))&amp;")",IF($D72&lt;1.8,"Nascent",IF($D72&lt;2.6,"Emerging",IF($D72&lt;3.4,"Established",IF($D72&lt;4.2,"Advanced","Transformative"))))))</f>
+        <f aca="false">IF($D72="","Not rated",IF((COUNTIFS($C$5:$C$61,$A72,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")+$I72+$J72)&gt;($C72-COUNTIFS($C$5:$C$61,$A72,$S$5:$S$61,"Judged",$T$5:$T$61,"&gt;0")),"("&amp;IF($D72&lt;1.5,"Nascent",IF($D72&lt;2.5,"Emerging",IF($D72&lt;3.5,"Established",IF($D72&lt;4.5,"Advanced","Transformative"))))&amp;")",IF($D72&lt;1.5,"Nascent",IF($D72&lt;2.5,"Emerging",IF($D72&lt;3.5,"Established",IF($D72&lt;4.5,"Advanced","Transformative"))))))</f>
         <v>Established</v>
       </c>
       <c r="F72" s="15" t="n">

--- a/gauntlet/loop-1/workbooks-v1.7/DAMM-v1.7-Scoring-Workbook-Nigeria.xlsx
+++ b/gauntlet/loop-1/workbooks-v1.7/DAMM-v1.7-Scoring-Workbook-Nigeria.xlsx
@@ -180,7 +180,7 @@
     <t xml:space="preserve">Readiness threshold</t>
   </si>
   <si>
-    <t xml:space="preserve">A use-case column whose bearing indicators average below this reads Partial.</t>
+    <t xml:space="preserve">A use-case column whose bearing indicators average below this reads Partial. Set to the Established band's lower edge.</t>
   </si>
   <si>
     <t xml:space="preserve">Leapfrog threshold</t>
@@ -2231,11 +2231,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="54620785"/>
-        <c:axId val="38812882"/>
+        <c:axId val="26521634"/>
+        <c:axId val="30134122"/>
       </c:radarChart>
       <c:catAx>
-        <c:axId val="54620785"/>
+        <c:axId val="26521634"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2265,7 +2265,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="38812882"/>
+        <c:crossAx val="30134122"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2273,7 +2273,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="38812882"/>
+        <c:axId val="30134122"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="5"/>
@@ -2318,7 +2318,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="54620785"/>
+        <c:crossAx val="26521634"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2538,11 +2538,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="41973315"/>
-        <c:axId val="90346970"/>
+        <c:axId val="14373457"/>
+        <c:axId val="82547654"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="41973315"/>
+        <c:axId val="14373457"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2575,7 +2575,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90346970"/>
+        <c:crossAx val="82547654"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2583,7 +2583,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="90346970"/>
+        <c:axId val="82547654"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2626,7 +2626,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="41973315"/>
+        <c:crossAx val="14373457"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3200,11 +3200,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="48254809"/>
-        <c:axId val="11868081"/>
+        <c:axId val="38796314"/>
+        <c:axId val="98813838"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="48254809"/>
+        <c:axId val="38796314"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3237,7 +3237,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="11868081"/>
+        <c:crossAx val="98813838"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3245,7 +3245,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="11868081"/>
+        <c:axId val="98813838"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3288,7 +3288,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="48254809"/>
+        <c:crossAx val="38796314"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3490,11 +3490,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="55379877"/>
-        <c:axId val="74667011"/>
+        <c:axId val="17662326"/>
+        <c:axId val="64937031"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="55379877"/>
+        <c:axId val="17662326"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3527,7 +3527,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74667011"/>
+        <c:crossAx val="64937031"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3535,7 +3535,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="74667011"/>
+        <c:axId val="64937031"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="5"/>
@@ -3579,7 +3579,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="55379877"/>
+        <c:crossAx val="17662326"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3787,11 +3787,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="40908087"/>
-        <c:axId val="7955604"/>
+        <c:axId val="94443322"/>
+        <c:axId val="84119735"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="40908087"/>
+        <c:axId val="94443322"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3824,7 +3824,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="7955604"/>
+        <c:crossAx val="84119735"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3832,7 +3832,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="7955604"/>
+        <c:axId val="84119735"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3875,7 +3875,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="40908087"/>
+        <c:crossAx val="94443322"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4113,11 +4113,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="70172770"/>
-        <c:axId val="97576656"/>
+        <c:axId val="81968974"/>
+        <c:axId val="97266344"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="70172770"/>
+        <c:axId val="81968974"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4150,7 +4150,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="97576656"/>
+        <c:crossAx val="97266344"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4158,7 +4158,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="97576656"/>
+        <c:axId val="97266344"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4201,7 +4201,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="70172770"/>
+        <c:crossAx val="81968974"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -6217,7 +6217,7 @@
         <v>46</v>
       </c>
       <c r="C4" s="3" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="D4" s="13" t="s">
         <v>47</v>

--- a/gauntlet/loop-1/workbooks-v1.7/DAMM-v1.7-Scoring-Workbook-Nigeria.xlsx
+++ b/gauntlet/loop-1/workbooks-v1.7/DAMM-v1.7-Scoring-Workbook-Nigeria.xlsx
@@ -1575,7 +1575,7 @@
     <t xml:space="preserve">Use case area</t>
   </si>
   <si>
-    <t xml:space="preserve">Mean of bearing indicators</t>
+    <t xml:space="preserve">Mean of enabling indicators</t>
   </si>
   <si>
     <t xml:space="preserve">Blocking / limiting factor</t>
@@ -2231,11 +2231,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="26521634"/>
-        <c:axId val="30134122"/>
+        <c:axId val="38929214"/>
+        <c:axId val="36395245"/>
       </c:radarChart>
       <c:catAx>
-        <c:axId val="26521634"/>
+        <c:axId val="38929214"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2265,7 +2265,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="30134122"/>
+        <c:crossAx val="36395245"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2273,7 +2273,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="30134122"/>
+        <c:axId val="36395245"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="5"/>
@@ -2318,7 +2318,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="26521634"/>
+        <c:crossAx val="38929214"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2538,11 +2538,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="14373457"/>
-        <c:axId val="82547654"/>
+        <c:axId val="63847333"/>
+        <c:axId val="99870415"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="14373457"/>
+        <c:axId val="63847333"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2575,7 +2575,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="82547654"/>
+        <c:crossAx val="99870415"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2583,7 +2583,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="82547654"/>
+        <c:axId val="99870415"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2626,7 +2626,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="14373457"/>
+        <c:crossAx val="63847333"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3200,11 +3200,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="38796314"/>
-        <c:axId val="98813838"/>
+        <c:axId val="25966483"/>
+        <c:axId val="78822462"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="38796314"/>
+        <c:axId val="25966483"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3237,7 +3237,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="98813838"/>
+        <c:crossAx val="78822462"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3245,7 +3245,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="98813838"/>
+        <c:axId val="78822462"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3288,7 +3288,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="38796314"/>
+        <c:crossAx val="25966483"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3490,11 +3490,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="17662326"/>
-        <c:axId val="64937031"/>
+        <c:axId val="70965263"/>
+        <c:axId val="25672901"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="17662326"/>
+        <c:axId val="70965263"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3527,7 +3527,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="64937031"/>
+        <c:crossAx val="25672901"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3535,7 +3535,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="64937031"/>
+        <c:axId val="25672901"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="5"/>
@@ -3579,7 +3579,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="17662326"/>
+        <c:crossAx val="70965263"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3787,11 +3787,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="94443322"/>
-        <c:axId val="84119735"/>
+        <c:axId val="92164822"/>
+        <c:axId val="18771388"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="94443322"/>
+        <c:axId val="92164822"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3824,7 +3824,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="84119735"/>
+        <c:crossAx val="18771388"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3832,7 +3832,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="84119735"/>
+        <c:axId val="18771388"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3875,7 +3875,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="94443322"/>
+        <c:crossAx val="92164822"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4113,11 +4113,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="81968974"/>
-        <c:axId val="97266344"/>
+        <c:axId val="13136740"/>
+        <c:axId val="324913"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="81968974"/>
+        <c:axId val="13136740"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4150,7 +4150,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="97266344"/>
+        <c:crossAx val="324913"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4158,7 +4158,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="97266344"/>
+        <c:axId val="324913"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4201,7 +4201,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="81968974"/>
+        <c:crossAx val="13136740"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12221,8 +12221,8 @@
         <v>514</v>
       </c>
       <c r="B102" s="15" t="n">
-        <f aca="false">IFERROR(ROUND(AVERAGEIF(V$5:V$61,1,$T$5:$T$61),2),"")</f>
-        <v>2.72</v>
+        <f aca="false">IFERROR(ROUND(AVERAGEIFS($T$5:$T$61,V$5:V$61,1,$C$5:$C$61,"&lt;&gt;A1",$C$5:$C$61,"&lt;&gt;O1"),2),"")</f>
+        <v>2.71</v>
       </c>
       <c r="C102" s="9" t="str">
         <f aca="false">IF(OR($D$86="Absent",$D$87="Absent",$D$88="Absent",$D$94="Absent"),"Blocked",IF(OR($D$86="Unverified",$D$87="Unverified",$D$88="Unverified",$D$94="Unverified"),"Unverified",IF(OR(OR($D$94="Present (narrow)"),$B102&lt;Config!$C$4,OR($D$86="Present (narrow)",$D$87="Present (narrow)",$D$88="Present (narrow)")),"Partial","Ready")))</f>
@@ -12238,8 +12238,8 @@
         <v>515</v>
       </c>
       <c r="B103" s="15" t="n">
-        <f aca="false">IFERROR(ROUND(AVERAGEIF(W$5:W$61,1,$T$5:$T$61),2),"")</f>
-        <v>2.69</v>
+        <f aca="false">IFERROR(ROUND(AVERAGEIFS($T$5:$T$61,W$5:W$61,1,$C$5:$C$61,"&lt;&gt;A1",$C$5:$C$61,"&lt;&gt;O1"),2),"")</f>
+        <v>2.68</v>
       </c>
       <c r="C103" s="9" t="str">
         <f aca="false">IF(OR($D$86="Absent",$D$87="Absent",$D$88="Absent"),"Blocked",IF(OR($D$86="Unverified",$D$87="Unverified",$D$88="Unverified"),"Unverified",IF(OR($B103&lt;Config!$C$4,OR($D$86="Present (narrow)",$D$87="Present (narrow)",$D$88="Present (narrow)")),"Partial","Ready")))</f>
@@ -12255,8 +12255,8 @@
         <v>516</v>
       </c>
       <c r="B104" s="15" t="n">
-        <f aca="false">IFERROR(ROUND(AVERAGEIF(X$5:X$61,1,$T$5:$T$61),2),"")</f>
-        <v>2.58</v>
+        <f aca="false">IFERROR(ROUND(AVERAGEIFS($T$5:$T$61,X$5:X$61,1,$C$5:$C$61,"&lt;&gt;A1",$C$5:$C$61,"&lt;&gt;O1"),2),"")</f>
+        <v>2.64</v>
       </c>
       <c r="C104" s="9" t="str">
         <f aca="false">IF(OR($D$86="Absent",$D$87="Absent",$D$88="Absent"),"Blocked",IF(OR($D$86="Unverified",$D$87="Unverified",$D$88="Unverified"),"Unverified",IF(OR($B104&lt;Config!$C$4,OR($D$86="Present (narrow)",$D$87="Present (narrow)",$D$88="Present (narrow)")),"Partial","Ready")))</f>
@@ -12272,8 +12272,8 @@
         <v>517</v>
       </c>
       <c r="B105" s="15" t="n">
-        <f aca="false">IFERROR(ROUND(AVERAGEIF(Y$5:Y$61,1,$T$5:$T$61),2),"")</f>
-        <v>2.63</v>
+        <f aca="false">IFERROR(ROUND(AVERAGEIFS($T$5:$T$61,Y$5:Y$61,1,$C$5:$C$61,"&lt;&gt;A1",$C$5:$C$61,"&lt;&gt;O1"),2),"")</f>
+        <v>2.61</v>
       </c>
       <c r="C105" s="9" t="str">
         <f aca="false">IF(OR($D$86="Absent",$D$87="Absent",$D$88="Absent"),"Blocked",IF(OR($D$86="Unverified",$D$87="Unverified",$D$88="Unverified"),"Unverified",IF(OR($B105&lt;Config!$C$4,OR($D$86="Present (narrow)",$D$87="Present (narrow)",$D$88="Present (narrow)")),"Partial","Ready")))</f>
@@ -12289,7 +12289,7 @@
         <v>518</v>
       </c>
       <c r="B106" s="15" t="n">
-        <f aca="false">IFERROR(ROUND(AVERAGEIF(Z$5:Z$61,1,$T$5:$T$61),2),"")</f>
+        <f aca="false">IFERROR(ROUND(AVERAGEIFS($T$5:$T$61,Z$5:Z$61,1,$C$5:$C$61,"&lt;&gt;A1",$C$5:$C$61,"&lt;&gt;O1"),2),"")</f>
         <v>2.5</v>
       </c>
       <c r="C106" s="9" t="str">
@@ -12306,8 +12306,8 @@
         <v>519</v>
       </c>
       <c r="B107" s="15" t="n">
-        <f aca="false">IFERROR(ROUND(AVERAGEIF(AA$5:AA$61,1,$T$5:$T$61),2),"")</f>
-        <v>2.59</v>
+        <f aca="false">IFERROR(ROUND(AVERAGEIFS($T$5:$T$61,AA$5:AA$61,1,$C$5:$C$61,"&lt;&gt;A1",$C$5:$C$61,"&lt;&gt;O1"),2),"")</f>
+        <v>2.57</v>
       </c>
       <c r="C107" s="9" t="str">
         <f aca="false">IF(OR($D$86="Absent",$D$87="Absent",$D$88="Absent",$D$89="Absent",$D$90="Absent",$D$91="Absent",$D$97="Absent"),"Blocked",IF(OR($D$86="Unverified",$D$87="Unverified",$D$88="Unverified",$D$89="Unverified",$D$90="Unverified",$D$91="Unverified",$D$97="Unverified"),"Unverified",IF(OR(OR($D$89="Present (narrow)",$D$90="Present (narrow)",$D$91="Present (narrow)",$D$97="Present (narrow)"),$B107&lt;Config!$C$4,OR($D$86="Present (narrow)",$D$87="Present (narrow)",$D$88="Present (narrow)")),"Partial","Ready")))</f>

--- a/gauntlet/loop-1/workbooks-v1.7/DAMM-v1.7-Scoring-Workbook-Nigeria.xlsx
+++ b/gauntlet/loop-1/workbooks-v1.7/DAMM-v1.7-Scoring-Workbook-Nigeria.xlsx
@@ -234,10 +234,10 @@
     <t xml:space="preserve">AI-enabled services</t>
   </si>
   <si>
-    <t xml:space="preserve">7.12 binds AGI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ruling pending ratification: the consent-and-rights prerequisite binds the agricultural-intelligence column.</t>
+    <t xml:space="preserve">7.12 binds ADV, SMF, FIN, AGI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ruling 13.4: the consent-and-rights prerequisite binds the agricultural-intelligence column.</t>
   </si>
   <si>
     <t xml:space="preserve">The shared ladder — scoring an indicator that is not a measurement</t>
@@ -1365,7 +1365,7 @@
     <t xml:space="preserve">AI</t>
   </si>
   <si>
-    <t xml:space="preserve">UC:AI</t>
+    <t xml:space="preserve">UC:ADV,SMF,FIN,AGI</t>
   </si>
   <si>
     <t xml:space="preserve">General cross-sector AI/automated-decision safeguards adopted and in force; nothing agriculture-specific. NDPC General Application and Implementation Directive (GAID) 2025 under NDPA 2023 (document dated 20 Mar 2025; law</t>
@@ -1566,7 +1566,7 @@
     <t xml:space="preserve">Use case: ADV</t>
   </si>
   <si>
-    <t xml:space="preserve">Use case: AI-enabled (binds AGI)</t>
+    <t xml:space="preserve">Use case: personal or farm-level data (ADV, SMF, FIN, AGI)</t>
   </si>
   <si>
     <t xml:space="preserve">Use-case readiness  (feeds Playbook Step 2B — Digital Readiness)</t>
@@ -2231,11 +2231,11 @@
             </c:numRef>
           </c:val>
         </c:ser>
-        <c:axId val="38929214"/>
-        <c:axId val="36395245"/>
+        <c:axId val="56047114"/>
+        <c:axId val="73821203"/>
       </c:radarChart>
       <c:catAx>
-        <c:axId val="38929214"/>
+        <c:axId val="56047114"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -2265,7 +2265,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="36395245"/>
+        <c:crossAx val="73821203"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2273,7 +2273,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="36395245"/>
+        <c:axId val="73821203"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="5"/>
@@ -2318,7 +2318,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="38929214"/>
+        <c:crossAx val="56047114"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -2538,11 +2538,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="63847333"/>
-        <c:axId val="99870415"/>
+        <c:axId val="75837858"/>
+        <c:axId val="80006265"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="63847333"/>
+        <c:axId val="75837858"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2575,7 +2575,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99870415"/>
+        <c:crossAx val="80006265"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2583,7 +2583,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="99870415"/>
+        <c:axId val="80006265"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2626,7 +2626,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="63847333"/>
+        <c:crossAx val="75837858"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3200,11 +3200,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="25966483"/>
-        <c:axId val="78822462"/>
+        <c:axId val="44102595"/>
+        <c:axId val="2233059"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="25966483"/>
+        <c:axId val="44102595"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3237,7 +3237,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="78822462"/>
+        <c:crossAx val="2233059"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3245,7 +3245,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="78822462"/>
+        <c:axId val="2233059"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3288,7 +3288,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="25966483"/>
+        <c:crossAx val="44102595"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3490,11 +3490,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="70965263"/>
-        <c:axId val="25672901"/>
+        <c:axId val="87693764"/>
+        <c:axId val="60571572"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="70965263"/>
+        <c:axId val="87693764"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3527,7 +3527,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="25672901"/>
+        <c:crossAx val="60571572"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3535,7 +3535,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="25672901"/>
+        <c:axId val="60571572"/>
         <c:scaling>
           <c:orientation val="minMax"/>
           <c:max val="5"/>
@@ -3579,7 +3579,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="70965263"/>
+        <c:crossAx val="87693764"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3787,11 +3787,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="92164822"/>
-        <c:axId val="18771388"/>
+        <c:axId val="68505003"/>
+        <c:axId val="56543627"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="92164822"/>
+        <c:axId val="68505003"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3824,7 +3824,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="18771388"/>
+        <c:crossAx val="56543627"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3832,7 +3832,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="18771388"/>
+        <c:axId val="56543627"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3875,7 +3875,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="92164822"/>
+        <c:crossAx val="68505003"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4113,11 +4113,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="13136740"/>
-        <c:axId val="324913"/>
+        <c:axId val="54337746"/>
+        <c:axId val="86183094"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="13136740"/>
+        <c:axId val="54337746"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4150,7 +4150,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="324913"/>
+        <c:crossAx val="86183094"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4158,7 +4158,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="324913"/>
+        <c:axId val="86183094"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4201,7 +4201,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="13136740"/>
+        <c:crossAx val="54337746"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12225,11 +12225,11 @@
         <v>2.71</v>
       </c>
       <c r="C102" s="9" t="str">
-        <f aca="false">IF(OR($D$86="Absent",$D$87="Absent",$D$88="Absent",$D$94="Absent"),"Blocked",IF(OR($D$86="Unverified",$D$87="Unverified",$D$88="Unverified",$D$94="Unverified"),"Unverified",IF(OR(OR($D$94="Present (narrow)"),$B102&lt;Config!$C$4,OR($D$86="Present (narrow)",$D$87="Present (narrow)",$D$88="Present (narrow)")),"Partial","Ready")))</f>
+        <f aca="false">IF(OR($D$86="Absent",$D$87="Absent",$D$88="Absent",$D$94="Absent",$D$97="Absent"),"Blocked",IF(OR($D$86="Unverified",$D$87="Unverified",$D$88="Unverified",$D$94="Unverified",$D$97="Unverified"),"Unverified",IF(OR(OR($D$94="Present (narrow)",$D$97="Present (narrow)"),$B102&lt;Config!$C$4,OR($D$86="Present (narrow)",$D$87="Present (narrow)",$D$88="Present (narrow)")),"Partial","Ready")))</f>
         <v>Partial</v>
       </c>
       <c r="D102" s="10" t="str">
-        <f aca="false">IF($C102="Ready","",IF(TRIM(IF($D$86&lt;&gt;"Present",$A$86&amp;" ","")&amp;IF($D$87&lt;&gt;"Present",$A$87&amp;" ","")&amp;IF($D$88&lt;&gt;"Present",$A$88&amp;" ","")&amp;IF($D$94&lt;&gt;"Present",$A$94&amp;" ",""))&lt;&gt;"",TRIM(IF($D$86&lt;&gt;"Present",$A$86&amp;" ","")&amp;IF($D$87&lt;&gt;"Present",$A$87&amp;" ","")&amp;IF($D$88&lt;&gt;"Present",$A$88&amp;" ","")&amp;IF($D$94&lt;&gt;"Present",$A$94&amp;" ","")),IF($B102&lt;Config!$C$4,"thin enablers (mean below "&amp;TEXT(Config!$C$4,"0.0")&amp;")","")))</f>
+        <f aca="false">IF($C102="Ready","",IF(TRIM(IF($D$86&lt;&gt;"Present",$A$86&amp;" ","")&amp;IF($D$87&lt;&gt;"Present",$A$87&amp;" ","")&amp;IF($D$88&lt;&gt;"Present",$A$88&amp;" ","")&amp;IF($D$94&lt;&gt;"Present",$A$94&amp;" ","")&amp;IF($D$97&lt;&gt;"Present",$A$97&amp;" ",""))&lt;&gt;"",TRIM(IF($D$86&lt;&gt;"Present",$A$86&amp;" ","")&amp;IF($D$87&lt;&gt;"Present",$A$87&amp;" ","")&amp;IF($D$88&lt;&gt;"Present",$A$88&amp;" ","")&amp;IF($D$94&lt;&gt;"Present",$A$94&amp;" ","")&amp;IF($D$97&lt;&gt;"Present",$A$97&amp;" ","")),IF($B102&lt;Config!$C$4,"thin enablers (mean below "&amp;TEXT(Config!$C$4,"0.0")&amp;")","")))</f>
         <v>2.9</v>
       </c>
     </row>
@@ -12242,11 +12242,11 @@
         <v>2.68</v>
       </c>
       <c r="C103" s="9" t="str">
-        <f aca="false">IF(OR($D$86="Absent",$D$87="Absent",$D$88="Absent"),"Blocked",IF(OR($D$86="Unverified",$D$87="Unverified",$D$88="Unverified"),"Unverified",IF(OR($B103&lt;Config!$C$4,OR($D$86="Present (narrow)",$D$87="Present (narrow)",$D$88="Present (narrow)")),"Partial","Ready")))</f>
+        <f aca="false">IF(OR($D$86="Absent",$D$87="Absent",$D$88="Absent",$D$97="Absent"),"Blocked",IF(OR($D$86="Unverified",$D$87="Unverified",$D$88="Unverified",$D$97="Unverified"),"Unverified",IF(OR(OR($D$97="Present (narrow)"),$B103&lt;Config!$C$4,OR($D$86="Present (narrow)",$D$87="Present (narrow)",$D$88="Present (narrow)")),"Partial","Ready")))</f>
         <v>Partial</v>
       </c>
       <c r="D103" s="10" t="str">
-        <f aca="false">IF($C103="Ready","",IF(TRIM(IF($D$86&lt;&gt;"Present",$A$86&amp;" ","")&amp;IF($D$87&lt;&gt;"Present",$A$87&amp;" ","")&amp;IF($D$88&lt;&gt;"Present",$A$88&amp;" ",""))&lt;&gt;"",TRIM(IF($D$86&lt;&gt;"Present",$A$86&amp;" ","")&amp;IF($D$87&lt;&gt;"Present",$A$87&amp;" ","")&amp;IF($D$88&lt;&gt;"Present",$A$88&amp;" ","")),IF($B103&lt;Config!$C$4,"thin enablers (mean below "&amp;TEXT(Config!$C$4,"0.0")&amp;")","")))</f>
+        <f aca="false">IF($C103="Ready","",IF(TRIM(IF($D$86&lt;&gt;"Present",$A$86&amp;" ","")&amp;IF($D$87&lt;&gt;"Present",$A$87&amp;" ","")&amp;IF($D$88&lt;&gt;"Present",$A$88&amp;" ","")&amp;IF($D$97&lt;&gt;"Present",$A$97&amp;" ",""))&lt;&gt;"",TRIM(IF($D$86&lt;&gt;"Present",$A$86&amp;" ","")&amp;IF($D$87&lt;&gt;"Present",$A$87&amp;" ","")&amp;IF($D$88&lt;&gt;"Present",$A$88&amp;" ","")&amp;IF($D$97&lt;&gt;"Present",$A$97&amp;" ","")),IF($B103&lt;Config!$C$4,"thin enablers (mean below "&amp;TEXT(Config!$C$4,"0.0")&amp;")","")))</f>
         <v>2.9</v>
       </c>
     </row>
@@ -12293,11 +12293,11 @@
         <v>2.5</v>
       </c>
       <c r="C106" s="9" t="str">
-        <f aca="false">IF(OR($D$86="Absent",$D$87="Absent",$D$88="Absent",$D$89="Absent",$D$92="Absent",$D$96="Absent"),"Blocked",IF(OR($D$86="Unverified",$D$87="Unverified",$D$88="Unverified",$D$89="Unverified",$D$92="Unverified",$D$96="Unverified"),"Unverified",IF(OR(OR($D$89="Present (narrow)",$D$92="Present (narrow)",$D$96="Present (narrow)"),$B106&lt;Config!$C$4,OR($D$86="Present (narrow)",$D$87="Present (narrow)",$D$88="Present (narrow)")),"Partial","Ready")))</f>
+        <f aca="false">IF(OR($D$86="Absent",$D$87="Absent",$D$88="Absent",$D$89="Absent",$D$92="Absent",$D$96="Absent",$D$97="Absent"),"Blocked",IF(OR($D$86="Unverified",$D$87="Unverified",$D$88="Unverified",$D$89="Unverified",$D$92="Unverified",$D$96="Unverified",$D$97="Unverified"),"Unverified",IF(OR(OR($D$89="Present (narrow)",$D$92="Present (narrow)",$D$96="Present (narrow)",$D$97="Present (narrow)"),$B106&lt;Config!$C$4,OR($D$86="Present (narrow)",$D$87="Present (narrow)",$D$88="Present (narrow)")),"Partial","Ready")))</f>
         <v>Partial</v>
       </c>
       <c r="D106" s="10" t="str">
-        <f aca="false">IF($C106="Ready","",IF(TRIM(IF($D$86&lt;&gt;"Present",$A$86&amp;" ","")&amp;IF($D$87&lt;&gt;"Present",$A$87&amp;" ","")&amp;IF($D$88&lt;&gt;"Present",$A$88&amp;" ","")&amp;IF($D$89&lt;&gt;"Present",$A$89&amp;" ","")&amp;IF($D$92&lt;&gt;"Present",$A$92&amp;" ","")&amp;IF($D$96&lt;&gt;"Present",$A$96&amp;" ",""))&lt;&gt;"",TRIM(IF($D$86&lt;&gt;"Present",$A$86&amp;" ","")&amp;IF($D$87&lt;&gt;"Present",$A$87&amp;" ","")&amp;IF($D$88&lt;&gt;"Present",$A$88&amp;" ","")&amp;IF($D$89&lt;&gt;"Present",$A$89&amp;" ","")&amp;IF($D$92&lt;&gt;"Present",$A$92&amp;" ","")&amp;IF($D$96&lt;&gt;"Present",$A$96&amp;" ","")),IF($B106&lt;Config!$C$4,"thin enablers (mean below "&amp;TEXT(Config!$C$4,"0.0")&amp;")","")))</f>
+        <f aca="false">IF($C106="Ready","",IF(TRIM(IF($D$86&lt;&gt;"Present",$A$86&amp;" ","")&amp;IF($D$87&lt;&gt;"Present",$A$87&amp;" ","")&amp;IF($D$88&lt;&gt;"Present",$A$88&amp;" ","")&amp;IF($D$89&lt;&gt;"Present",$A$89&amp;" ","")&amp;IF($D$92&lt;&gt;"Present",$A$92&amp;" ","")&amp;IF($D$96&lt;&gt;"Present",$A$96&amp;" ","")&amp;IF($D$97&lt;&gt;"Present",$A$97&amp;" ",""))&lt;&gt;"",TRIM(IF($D$86&lt;&gt;"Present",$A$86&amp;" ","")&amp;IF($D$87&lt;&gt;"Present",$A$87&amp;" ","")&amp;IF($D$88&lt;&gt;"Present",$A$88&amp;" ","")&amp;IF($D$89&lt;&gt;"Present",$A$89&amp;" ","")&amp;IF($D$92&lt;&gt;"Present",$A$92&amp;" ","")&amp;IF($D$96&lt;&gt;"Present",$A$96&amp;" ","")&amp;IF($D$97&lt;&gt;"Present",$A$97&amp;" ","")),IF($B106&lt;Config!$C$4,"thin enablers (mean below "&amp;TEXT(Config!$C$4,"0.0")&amp;")","")))</f>
         <v>2.9 3.3</v>
       </c>
     </row>
